--- a/Dentists/web/public/resources/associate/associate-model.xlsx
+++ b/Dentists/web/public/resources/associate/associate-model.xlsx
@@ -23,8 +23,7 @@
     <definedName name="Class4Upper">Rates!$B$9</definedName>
     <definedName name="Class4RateLower">Rates!$B$10</definedName>
     <definedName name="Class4RateUpper">Rates!$B$11</definedName>
-    <definedName name="Class2Weekly">Rates!$B$12</definedName>
-    <definedName name="Class2Threshold">Rates!$B$13</definedName>
+    <definedName name="Class2Charge">Rates!$B$12</definedName>
     <definedName name="In_GrossFees">'Your figures'!$B$3</definedName>
     <definedName name="In_AssocPct">'Your figures'!$B$4</definedName>
     <definedName name="In_LabPct">'Your figures'!$B$5</definedName>
@@ -45,9 +44,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="58">
-  <si>
-    <t>Locked rates: do not edit (2025/26)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="58">
+  <si>
+    <t>Locked rates: do not edit (2026/27)</t>
   </si>
   <si>
     <t>Income tax: personal allowance (GBP)</t>
@@ -80,10 +79,7 @@
     <t>Class 4 NI: upper rate (above upper limit)</t>
   </si>
   <si>
-    <t>Class 2 NI: weekly amount (GBP)</t>
-  </si>
-  <si>
-    <t>Class 2 NI: small profits threshold (GBP)</t>
+    <t>Class 2 NI: weekly amount (removed from 6 Apr 2024)</t>
   </si>
   <si>
     <t>Your figures: edit the highlighted cells</t>
@@ -137,12 +133,15 @@
     <t>Class 4 NI</t>
   </si>
   <si>
+    <t>Class 2 NI (not payable from 6 Apr 2024)</t>
+  </si>
+  <si>
+    <t>Total tax and NI</t>
+  </si>
+  <si>
     <t>Class 2 NI</t>
   </si>
   <si>
-    <t>Total tax and NI</t>
-  </si>
-  <si>
     <t>Net cash</t>
   </si>
   <si>
@@ -167,7 +166,7 @@
     <t>This model shows your estimated take-home pay as a dental associate or locum,</t>
   </si>
   <si>
-    <t>after income tax, Class 4 NI and Class 2 NI, based on 2025/26 rates.</t>
+    <t>after income tax, Class 4 NI and Class 2 NI, based on 2026/27 rates.</t>
   </si>
   <si>
     <t>How to use:</t>
@@ -182,7 +181,7 @@
     <t>3. Every figure recalculates automatically.</t>
   </si>
   <si>
-    <t>The 'Rates' tab holds the locked 2025/26 rates. Do not edit it.</t>
+    <t>The 'Rates' tab holds the locked 2026/27 rates. Do not edit it.</t>
   </si>
   <si>
     <t>See 'Notes' for assumptions and limitations.</t>
@@ -191,7 +190,7 @@
     <t>Assumptions and limitations</t>
   </si>
   <si>
-    <t>2025/26 rates: income tax personal allowance GBP12,570; basic rate 20% to GBP50,270;</t>
+    <t>2026/27 rates: income tax personal allowance GBP12,570; basic rate 20% to GBP50,270;</t>
   </si>
   <si>
     <t>higher rate 40% to GBP125,140; additional rate 45% above.</t>
@@ -200,7 +199,7 @@
     <t>Class 4 NI: 6% between GBP12,570 and GBP50,270, 2% above.</t>
   </si>
   <si>
-    <t>Class 2 NI: GBP3.45/week (52 weeks) if profit exceeds the GBP6,725 small profits threshold.</t>
+    <t>Class 2 NI: not payable. The liability was removed from 6 April 2024; profits at or above the small profits threshold are treated as having paid it.</t>
   </si>
   <si>
     <t>Lab deduction: calculated as lab% of gross fees, then scaled by the associate percentage.</t>
@@ -678,7 +677,7 @@
   <sheetPr>
     <tabColor rgb="FF001b3d"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="52" style="1" customWidth="1"/>
@@ -776,15 +775,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="4">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4">
-        <v>6725</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -814,23 +805,23 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B1" s="6"/>
       <c r="D1" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E1" s="7"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" s="9">
         <v>120000</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3" s="10">
         <f>In_GrossFees</f>
@@ -838,13 +829,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="11">
         <v>50</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" s="10">
         <f>AssocShare</f>
@@ -852,13 +843,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="11">
         <v>8</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5" s="10">
         <f>LabDeduct</f>
@@ -866,13 +857,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" s="9">
         <v>3000</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="10">
         <f>In_Expenses</f>
@@ -880,13 +871,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="9">
         <v>0</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E7" s="10">
         <f>In_Pension</f>
@@ -894,7 +885,7 @@
     </row>
     <row r="8" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D8" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" s="13">
         <f>TaxableProfit</f>
@@ -902,7 +893,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="10">
         <f>In_GrossFees*(In_AssocPct/100)</f>
@@ -910,13 +901,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="10">
         <f>In_GrossFees*(In_LabPct/100)*(In_AssocPct/100)</f>
       </c>
       <c r="D10" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" s="10">
         <f>IncomeTax</f>
@@ -924,13 +915,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" s="10">
         <f>MAX(0,AssocShare-LabDeduct-In_Expenses)</f>
       </c>
       <c r="D11" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E11" s="10">
         <f>Class4</f>
@@ -938,13 +929,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" s="10">
         <f>MAX(0,ProfitBeforePension-In_Pension)</f>
       </c>
       <c r="D12" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E12" s="10">
         <f>Class2</f>
@@ -952,13 +943,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" s="10">
         <f>LET(tp,TaxableProfit,pa,IF(tp&gt;100000,MAX(0,PA-(tp-100000)/2),PA),t,MAX(0,tp-pa),basic,MIN(t,BasicLimit-PA),higher,MAX(0,MIN(t-basic,HigherLimit-BasicLimit)),additional,MAX(0,t-basic-higher),basic*IncomeBasic+higher*IncomeHigher+additional*IncomeAdditional)</f>
       </c>
       <c r="D13" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13" s="13">
         <f>TotalTax</f>
@@ -966,7 +957,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B14" s="10">
         <f>IF(TaxableProfit&lt;=Class4Lower,0,(MIN(TaxableProfit,Class4Upper)-Class4Lower)*Class4RateLower+MAX(0,TaxableProfit-Class4Upper)*Class4RateUpper)</f>
@@ -974,10 +965,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" s="10">
-        <f>IF(ProfitBeforePension&gt;Class2Threshold,52*Class2Weekly,0)</f>
+        <f>Class2Charge</f>
       </c>
       <c r="D15" s="12" t="s">
         <v>32</v>
@@ -988,7 +979,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="15">
         <f>IncomeTax+Class4+Class2</f>

--- a/Dentists/web/public/resources/associate/associate-model.xlsx
+++ b/Dentists/web/public/resources/associate/associate-model.xlsx
@@ -211,7 +211,7 @@
     <t>NHS Pension: treated as deductible from taxable profit (practitioner arrangement).</t>
   </si>
   <si>
-    <t>It reduces both income tax and Class 4 NI. Class 2 is based on profit before pension.</t>
+    <t>It reduces both income tax and Class 4 NI.</t>
   </si>
   <si>
     <t>This is a directional model. Your actual position depends on student loan repayments,</t>
